--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2011/CALIFORNIA_2011.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2011/CALIFORNIA_2011.xlsx
@@ -1687,7 +1687,7 @@
         <v>27</v>
       </c>
       <c r="D74">
-        <v>9.5947804394E-05</v>
+        <v>9.594780439400001E-05</v>
       </c>
     </row>
     <row r="75">
@@ -3271,7 +3271,7 @@
         <v>27</v>
       </c>
       <c r="D162">
-        <v>9.5947804394E-05</v>
+        <v>9.594780439400001E-05</v>
       </c>
     </row>
     <row r="163">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Temosachi</t>
+          <t>Temosachic</t>
         </is>
       </c>
       <c r="C195">
@@ -5028,7 +5028,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Gral. Simon Boivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C260">
@@ -5640,7 +5640,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C294">
@@ -8095,7 +8095,7 @@
         <v>27</v>
       </c>
       <c r="D430">
-        <v>9.5947804394E-05</v>
+        <v>9.594780439400001E-05</v>
       </c>
     </row>
     <row r="431">
@@ -13081,7 +13081,7 @@
         <v>27</v>
       </c>
       <c r="D707">
-        <v>9.5947804394E-05</v>
+        <v>9.594780439400001E-05</v>
       </c>
     </row>
     <row r="708">
@@ -13261,7 +13261,7 @@
         <v>27</v>
       </c>
       <c r="D717">
-        <v>9.5947804394E-05</v>
+        <v>9.594780439400001E-05</v>
       </c>
     </row>
     <row r="718">
@@ -13927,7 +13927,7 @@
         <v>274</v>
       </c>
       <c r="D754">
-        <v>0.000973692533484</v>
+        <v>0.0009736925334840002</v>
       </c>
     </row>
     <row r="755">
@@ -14503,7 +14503,7 @@
         <v>257</v>
       </c>
       <c r="D786">
-        <v>0.000913280952939</v>
+        <v>0.0009132809529390002</v>
       </c>
     </row>
     <row r="787">
@@ -16872,7 +16872,7 @@
       </c>
       <c r="B918" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C918">
@@ -19633,7 +19633,7 @@
         <v>27</v>
       </c>
       <c r="D1071">
-        <v>9.5947804394E-05</v>
+        <v>9.594780439400001E-05</v>
       </c>
     </row>
     <row r="1072">
@@ -20886,7 +20886,7 @@
       </c>
       <c r="B1141" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C1141">
@@ -20904,7 +20904,7 @@
       </c>
       <c r="B1142" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 26 -</t>
+          <t>San Juan Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C1142">
@@ -22614,7 +22614,7 @@
       </c>
       <c r="B1237" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C1237">
@@ -22632,7 +22632,7 @@
       </c>
       <c r="B1238" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 26 -</t>
+          <t>San Pedro Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C1238">
@@ -22830,7 +22830,7 @@
       </c>
       <c r="B1249" t="inlineStr">
         <is>
-          <t>San Pedro Totolapa</t>
+          <t>San Pedro Totolapam</t>
         </is>
       </c>
       <c r="C1249">
@@ -25854,7 +25854,7 @@
       </c>
       <c r="B1417" t="inlineStr">
         <is>
-          <t>Santo Domingo Tonaltepec</t>
+          <t>Santo Domingo Tomaltepec</t>
         </is>
       </c>
       <c r="C1417">
@@ -26275,7 +26275,7 @@
         <v>274</v>
       </c>
       <c r="D1440">
-        <v>0.000973692533484</v>
+        <v>0.0009736925334840002</v>
       </c>
     </row>
     <row r="1441">
@@ -26545,7 +26545,7 @@
         <v>263</v>
       </c>
       <c r="D1455">
-        <v>0.000934602687249</v>
+        <v>0.0009346026872490002</v>
       </c>
     </row>
     <row r="1456">
@@ -27852,7 +27852,7 @@
       </c>
       <c r="B1528" t="inlineStr">
         <is>
-          <t>General Felipe _Ngeles</t>
+          <t>General Felipe Angeles</t>
         </is>
       </c>
       <c r="C1528">
@@ -31405,7 +31405,7 @@
         <v>27</v>
       </c>
       <c r="D1725">
-        <v>9.5947804394E-05</v>
+        <v>9.594780439400001E-05</v>
       </c>
     </row>
     <row r="1726">
@@ -33637,7 +33637,7 @@
         <v>27</v>
       </c>
       <c r="D1849">
-        <v>9.5947804394E-05</v>
+        <v>9.594780439400001E-05</v>
       </c>
     </row>
     <row r="1850">
@@ -34260,7 +34260,7 @@
       </c>
       <c r="B1884" t="inlineStr">
         <is>
-          <t>Altzayanca</t>
+          <t>Atltzayanca</t>
         </is>
       </c>
       <c r="C1884">
@@ -34915,7 +34915,7 @@
         <v>27</v>
       </c>
       <c r="D1920">
-        <v>9.5947804394E-05</v>
+        <v>9.594780439400001E-05</v>
       </c>
     </row>
     <row r="1921">
@@ -35160,7 +35160,7 @@
       </c>
       <c r="B1934" t="inlineStr">
         <is>
-          <t>Yauhquemecan</t>
+          <t>Yauhquemehcan</t>
         </is>
       </c>
       <c r="C1934">
@@ -35455,7 +35455,7 @@
         <v>27</v>
       </c>
       <c r="D1950">
-        <v>9.5947804394E-05</v>
+        <v>9.594780439400001E-05</v>
       </c>
     </row>
     <row r="1951">
@@ -38490,7 +38490,7 @@
       </c>
       <c r="B2119" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C2119">
